--- a/Estimate_Packaging_Logs.xlsx
+++ b/Estimate_Packaging_Logs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Documents\GitHub\Siri_interprint_Estimate_MI2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAED369-3D67-4B26-8E01-251B29F19561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B430CC8-063A-4AE9-9BC4-7FBD6FC55105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="780" firstSheet="5" activeTab="10" xr2:uid="{2CF4C729-DE4F-435F-B5B7-05BD9BC7401D}"/>
   </bookViews>
@@ -179,7 +179,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="231">
   <si>
     <t xml:space="preserve">เลขที่ JOB </t>
   </si>
@@ -1005,25 +1005,6 @@
   </si>
   <si>
     <t>เพิ่ม field is_loss ใน tb_rfq</t>
-  </si>
-  <si>
-    <t>แก้ไขปัญหางานหลาย F เพิ่ม process material , other cost แบบไม่คงที่ คำนวณราคาไม่ถูกต้อง</t>
-  </si>
-  <si>
-    <t>เพิ่มเงื่อนไขการ summary ใน summarytotalprice</t>
-  </si>
-  <si>
-    <t>เพิ่มคอลัมน์ customer ใน export excel</t>
-  </si>
-  <si>
-    <t>อยากให้มีการทำ Profit Sharing ได้</t>
-  </si>
-  <si>
-    <t>- มีให้เลือกติ๊กว่าจะทำ Profit Sharing ไหม
-- การทำ profit sharing จะทำได้เฉพาะงานพิมพ์ Offset + ตัด 2
-- การทำ profit sharing จะเป็นการเพิ่มราคาไปในแต่ละ process บาง process 15-20%
-- การทำ profit sharing จะมี + เพิ่มไปอีก 0.05 % หรือ 5,000 บาทในตอนท้ายก่อนคิดราคาต่อชิ้น
-- ในหน้าเลือก RFQ จะมีแสดงบอกว่างานไหนทำ profit sharing</t>
   </si>
 </sst>
 </file>
@@ -1704,7 +1685,7 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1745,6 +1726,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1788,6 +1770,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
@@ -1826,7 +1810,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -1834,9 +1821,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1887,7 +1881,10 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1899,10 +1896,13 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1920,13 +1920,17 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1944,17 +1948,28 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2119,38 +2134,26 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4607,131 +4610,146 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="55" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" style="55" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="55" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="55" customWidth="1"/>
-    <col min="5" max="5" width="16.109375" style="91" customWidth="1"/>
-    <col min="6" max="6" width="64.77734375" style="55" customWidth="1"/>
-    <col min="7" max="7" width="26.44140625" style="96" customWidth="1"/>
-    <col min="8" max="16384" width="8.77734375" style="55"/>
+    <col min="1" max="1" width="6.109375" style="58" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" style="58" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="58" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="58" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" style="99" customWidth="1"/>
+    <col min="6" max="6" width="64.77734375" style="58" customWidth="1"/>
+    <col min="7" max="7" width="26.44140625" style="105" customWidth="1"/>
+    <col min="8" max="16384" width="8.77734375" style="58"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="96" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="96" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="C1" s="96" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="D1" s="96" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="100" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="96" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="95" t="s">
+      <c r="G1" s="104" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B2" s="54"/>
+      <c r="B2" s="57"/>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B3" s="54"/>
+      <c r="B3" s="57"/>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B4" s="54"/>
+      <c r="B4" s="57"/>
     </row>
     <row r="5" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B5" s="54"/>
+      <c r="B5" s="57"/>
     </row>
     <row r="6" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B6" s="54"/>
+      <c r="B6" s="57"/>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B7" s="54"/>
+      <c r="B7" s="57"/>
     </row>
     <row r="8" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B8" s="54"/>
+      <c r="B8" s="57"/>
     </row>
     <row r="9" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B9" s="54"/>
+      <c r="B9" s="120"/>
+      <c r="C9" s="121"/>
     </row>
     <row r="10" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B10" s="54"/>
+      <c r="B10" s="120"/>
+      <c r="C10" s="121"/>
     </row>
     <row r="11" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B11" s="54"/>
+      <c r="B11" s="120"/>
+      <c r="C11" s="121"/>
     </row>
     <row r="12" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B12" s="54"/>
+      <c r="B12" s="120"/>
+      <c r="C12" s="121"/>
     </row>
     <row r="13" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B13" s="54"/>
+      <c r="B13" s="120"/>
+      <c r="C13" s="121"/>
     </row>
     <row r="14" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B14" s="54"/>
+      <c r="B14" s="120"/>
+      <c r="C14" s="121"/>
     </row>
     <row r="15" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B15" s="54"/>
+      <c r="B15" s="120"/>
+      <c r="C15" s="121"/>
     </row>
     <row r="16" spans="1:7" ht="19.95" customHeight="1">
-      <c r="B16" s="54"/>
+      <c r="B16" s="120"/>
+      <c r="C16" s="121"/>
     </row>
     <row r="17" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B17" s="54"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="96"/>
-      <c r="G17" s="55"/>
+      <c r="B17" s="120"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="58"/>
     </row>
     <row r="18" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B18" s="54"/>
+      <c r="B18" s="120"/>
+      <c r="C18" s="121"/>
     </row>
     <row r="19" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B19" s="54"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="121"/>
     </row>
     <row r="20" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B20" s="54"/>
+      <c r="B20" s="120"/>
+      <c r="C20" s="121"/>
     </row>
     <row r="21" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B21" s="54"/>
+      <c r="B21" s="120"/>
+      <c r="C21" s="121"/>
     </row>
     <row r="22" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B22" s="54"/>
+      <c r="B22" s="120"/>
+      <c r="C22" s="121"/>
     </row>
     <row r="23" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B23" s="54"/>
+      <c r="B23" s="120"/>
+      <c r="C23" s="121"/>
     </row>
     <row r="24" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B24" s="54"/>
+      <c r="B24" s="120"/>
+      <c r="C24" s="121"/>
     </row>
     <row r="25" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B25" s="54"/>
+      <c r="B25" s="57"/>
     </row>
     <row r="26" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B26" s="54"/>
-      <c r="E26" s="97"/>
+      <c r="B26" s="57"/>
+      <c r="E26" s="106"/>
     </row>
     <row r="27" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B27" s="54"/>
-      <c r="E27" s="97"/>
+      <c r="B27" s="57"/>
+      <c r="E27" s="106"/>
     </row>
     <row r="28" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B28" s="54"/>
+      <c r="B28" s="57"/>
     </row>
     <row r="29" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B29" s="54"/>
+      <c r="B29" s="57"/>
     </row>
     <row r="32" spans="2:7" ht="19.95" customHeight="1">
-      <c r="B32" s="54"/>
+      <c r="B32" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4744,190 +4762,195 @@
   <dimension ref="A1:F88"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="98"/>
+    <col min="1" max="1" width="8.77734375" style="107"/>
     <col min="2" max="2" width="74.5546875" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" customWidth="1"/>
+    <col min="5" max="5" width="19.44140625" style="110" customWidth="1"/>
     <col min="6" max="6" width="72.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="111" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="108" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="99" t="s">
+      <c r="C1" s="108" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="D1" s="108" t="s">
         <v>136</v>
       </c>
-      <c r="E1" s="100" t="s">
+      <c r="E1" s="109" t="s">
         <v>137</v>
       </c>
-      <c r="F1" s="99" t="s">
+      <c r="F1" s="108" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="98">
+      <c r="A2" s="122">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="71" t="s">
         <v>218</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="123">
         <v>44806</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="123">
         <v>44806</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="124" t="s">
         <v>219</v>
       </c>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="98">
+      <c r="A3" s="122">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="71" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="37">
+      <c r="C3" s="123">
         <v>44806</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D3" s="123">
         <v>44806</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="124" t="s">
         <v>219</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="71" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="98">
+      <c r="A4" s="122">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="71" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="123">
         <v>44832</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="123">
         <v>44854</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="124" t="s">
         <v>219</v>
       </c>
+      <c r="F4" s="71"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="98">
+      <c r="A5" s="122">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="71" t="s">
         <v>223</v>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="123">
         <v>44832</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="123">
         <v>44854</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="124" t="s">
         <v>219</v>
       </c>
+      <c r="F5" s="71"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="98">
+      <c r="A6" s="122">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="71" t="s">
         <v>224</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="123">
         <v>44841</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="123">
         <v>44854</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="124" t="s">
         <v>219</v>
       </c>
+      <c r="F6" s="71"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="98">
+      <c r="A7" s="122">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C7" s="123">
         <v>44858</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D7" s="123">
         <v>44858</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="124" t="s">
         <v>219</v>
       </c>
+      <c r="F7" s="71"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="98">
+      <c r="A8" s="122">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="71" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="37">
+      <c r="C8" s="123">
         <v>44861</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="38">
         <v>44867</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="124" t="s">
         <v>219</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="71" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="98">
+      <c r="A9" s="122">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="71" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="38">
         <v>44867</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="38">
         <v>44867</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="124" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="98">
+      <c r="A10" s="122">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="71" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="123">
         <v>44861</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="38">
         <v>44867</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="124" t="s">
         <v>219</v>
       </c>
       <c r="F10" t="s">
@@ -4935,286 +4958,316 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="98">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>231</v>
-      </c>
-      <c r="C11" s="37">
-        <v>44916</v>
-      </c>
-      <c r="D11" s="37">
-        <v>44916</v>
-      </c>
-      <c r="E11" t="s">
-        <v>219</v>
-      </c>
-      <c r="F11" t="s">
-        <v>232</v>
-      </c>
+      <c r="A11"/>
+      <c r="E11"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="98">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>233</v>
-      </c>
-      <c r="C12" s="37">
-        <v>44916</v>
-      </c>
-      <c r="D12" s="37">
-        <v>44916</v>
-      </c>
-      <c r="E12" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="106.8" customHeight="1">
-      <c r="A13" s="176">
-        <v>12</v>
-      </c>
-      <c r="B13" s="175" t="s">
-        <v>234</v>
-      </c>
-      <c r="C13" s="178">
-        <v>44995</v>
-      </c>
-      <c r="D13" s="178">
-        <v>45002</v>
-      </c>
-      <c r="E13" s="175" t="s">
-        <v>219</v>
-      </c>
-      <c r="F13" s="177" t="s">
-        <v>235</v>
-      </c>
+      <c r="A12"/>
+      <c r="E12"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13"/>
+      <c r="E13"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14"/>
+      <c r="E14"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15"/>
+      <c r="E15"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16"/>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="E16"/>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17"/>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="E17"/>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18"/>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="E18"/>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19"/>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="E19"/>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20"/>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="E20"/>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21"/>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="E21"/>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22"/>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="E22"/>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23"/>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="E23"/>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24"/>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="E24"/>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25"/>
-    </row>
-    <row r="26" spans="1:1">
+      <c r="E25"/>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26"/>
-    </row>
-    <row r="27" spans="1:1">
+      <c r="E26"/>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27"/>
-    </row>
-    <row r="28" spans="1:1">
+      <c r="E27"/>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28"/>
-    </row>
-    <row r="29" spans="1:1">
+      <c r="E28"/>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29"/>
-    </row>
-    <row r="30" spans="1:1">
+      <c r="E29"/>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30"/>
-    </row>
-    <row r="31" spans="1:1">
+      <c r="E30"/>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31"/>
-    </row>
-    <row r="32" spans="1:1">
+      <c r="E31"/>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32"/>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="E32"/>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33"/>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="E33"/>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34"/>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="E34"/>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35"/>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="E35"/>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36"/>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="E36"/>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37"/>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="E37"/>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38"/>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="E38"/>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39"/>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="E39"/>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40"/>
-    </row>
-    <row r="41" spans="1:1">
+      <c r="E40"/>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41"/>
-    </row>
-    <row r="42" spans="1:1">
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42"/>
-    </row>
-    <row r="43" spans="1:1">
+      <c r="E42"/>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43"/>
-    </row>
-    <row r="44" spans="1:1">
+      <c r="E43"/>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44"/>
-    </row>
-    <row r="45" spans="1:1">
+      <c r="E44"/>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45"/>
-    </row>
-    <row r="46" spans="1:1">
+      <c r="E45"/>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46"/>
-    </row>
-    <row r="47" spans="1:1">
+      <c r="E46"/>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47"/>
-    </row>
-    <row r="48" spans="1:1">
+      <c r="E47"/>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48"/>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="E48"/>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49"/>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="E49"/>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50"/>
-    </row>
-    <row r="51" spans="1:1">
+      <c r="E50"/>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51"/>
-    </row>
-    <row r="52" spans="1:1">
+      <c r="E51"/>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52"/>
-    </row>
-    <row r="53" spans="1:1">
+      <c r="E52"/>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53"/>
-    </row>
-    <row r="54" spans="1:1">
+      <c r="E53"/>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54"/>
-    </row>
-    <row r="55" spans="1:1">
+      <c r="E54"/>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55"/>
-    </row>
-    <row r="56" spans="1:1">
+      <c r="E55"/>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56"/>
-    </row>
-    <row r="57" spans="1:1">
+      <c r="E56"/>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57"/>
-    </row>
-    <row r="58" spans="1:1">
+      <c r="E57"/>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58"/>
-    </row>
-    <row r="59" spans="1:1">
+      <c r="E58"/>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59"/>
-    </row>
-    <row r="60" spans="1:1">
+      <c r="E59"/>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60"/>
-    </row>
-    <row r="61" spans="1:1">
+      <c r="E60"/>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61"/>
-    </row>
-    <row r="62" spans="1:1">
+      <c r="E61"/>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62"/>
-    </row>
-    <row r="63" spans="1:1">
+      <c r="E62"/>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63"/>
-    </row>
-    <row r="64" spans="1:1">
+      <c r="E63"/>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64"/>
-    </row>
-    <row r="65" spans="1:1">
+      <c r="E64"/>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65"/>
-    </row>
-    <row r="66" spans="1:1">
+      <c r="E65"/>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66"/>
-    </row>
-    <row r="67" spans="1:1">
+      <c r="E66"/>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67"/>
-    </row>
-    <row r="68" spans="1:1">
+      <c r="E67"/>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68"/>
-    </row>
-    <row r="69" spans="1:1">
+      <c r="E68"/>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69"/>
-    </row>
-    <row r="70" spans="1:1">
+      <c r="E69"/>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70"/>
-    </row>
-    <row r="71" spans="1:1">
+      <c r="E70"/>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71"/>
-    </row>
-    <row r="72" spans="1:1">
+      <c r="E71"/>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72"/>
-    </row>
-    <row r="73" spans="1:1">
+      <c r="E72"/>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73"/>
-    </row>
-    <row r="74" spans="1:1">
+      <c r="E73"/>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74"/>
-    </row>
-    <row r="75" spans="1:1">
+      <c r="E74"/>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75"/>
-    </row>
-    <row r="76" spans="1:1">
+      <c r="E75"/>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76"/>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="E76"/>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77"/>
-    </row>
-    <row r="78" spans="1:1">
+      <c r="E77"/>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78"/>
-    </row>
-    <row r="79" spans="1:1">
+      <c r="E78"/>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79"/>
-    </row>
-    <row r="80" spans="1:1">
+      <c r="E79"/>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80"/>
-    </row>
-    <row r="81" spans="1:1">
+      <c r="E80"/>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81"/>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="E81"/>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82"/>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="E82"/>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83"/>
-    </row>
-    <row r="84" spans="1:1">
+      <c r="E83"/>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84"/>
-    </row>
-    <row r="85" spans="1:1">
+      <c r="E84"/>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85"/>
-    </row>
-    <row r="86" spans="1:1">
+      <c r="E85"/>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86"/>
-    </row>
-    <row r="87" spans="1:1">
+      <c r="E86"/>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87"/>
-    </row>
-    <row r="88" spans="1:1">
+      <c r="E87"/>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88"/>
+      <c r="E88"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5245,14 +5298,14 @@
       </c>
     </row>
     <row r="3" spans="2:9" ht="17.55" customHeight="1">
-      <c r="B3" s="141" t="s">
+      <c r="B3" s="157" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
     </row>
     <row r="4" spans="2:9" ht="34.799999999999997" customHeight="1">
       <c r="H4" s="4" t="s">
@@ -5260,7 +5313,7 @@
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="36" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -5284,10 +5337,10 @@
       </c>
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="142" t="s">
+      <c r="G7" s="158" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="143"/>
+      <c r="H7" s="159"/>
       <c r="I7" s="12"/>
     </row>
     <row r="8" spans="2:9" ht="18.45" customHeight="1">
@@ -5298,12 +5351,12 @@
       <c r="D8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="144" t="s">
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="160" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="145"/>
+      <c r="H8" s="161"/>
       <c r="I8" s="12"/>
     </row>
     <row r="9" spans="2:9" ht="22.2" customHeight="1">
@@ -5314,10 +5367,10 @@
       <c r="D9" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="146"/>
-      <c r="H9" s="147"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="162"/>
+      <c r="H9" s="163"/>
       <c r="I9" s="12"/>
     </row>
     <row r="11" spans="2:9" ht="19.8">
@@ -5329,25 +5382,25 @@
       <c r="D12" s="6"/>
     </row>
     <row r="13" spans="2:9" ht="20.399999999999999" thickBot="1">
-      <c r="B13" s="148" t="s">
+      <c r="B13" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="149"/>
-      <c r="D13" s="154" t="s">
+      <c r="C13" s="165"/>
+      <c r="D13" s="170" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="155"/>
-      <c r="F13" s="155"/>
-      <c r="G13" s="155"/>
-      <c r="H13" s="156"/>
+      <c r="E13" s="171"/>
+      <c r="F13" s="171"/>
+      <c r="G13" s="171"/>
+      <c r="H13" s="172"/>
     </row>
     <row r="14" spans="2:9" ht="17.399999999999999">
-      <c r="B14" s="150"/>
-      <c r="C14" s="151"/>
-      <c r="D14" s="157" t="s">
+      <c r="B14" s="166"/>
+      <c r="C14" s="167"/>
+      <c r="D14" s="173" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="157" t="s">
+      <c r="E14" s="173" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="7" t="s">
@@ -5356,22 +5409,22 @@
       <c r="G14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="159" t="s">
+      <c r="H14" s="175" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="18" thickBot="1">
-      <c r="B15" s="152"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
+      <c r="B15" s="168"/>
+      <c r="C15" s="169"/>
+      <c r="D15" s="174"/>
+      <c r="E15" s="174"/>
       <c r="F15" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="160"/>
+      <c r="H15" s="176"/>
     </row>
     <row r="16" spans="2:9" ht="20.399999999999999" thickBot="1">
       <c r="B16" s="5">
@@ -5545,138 +5598,138 @@
       </c>
     </row>
     <row r="35" spans="2:8" ht="21" customHeight="1">
-      <c r="B35" s="24"/>
-      <c r="C35" s="114" t="s">
+      <c r="B35" s="25"/>
+      <c r="C35" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="114"/>
-      <c r="E35" s="114"/>
-      <c r="F35" s="114"/>
-      <c r="G35" s="114"/>
-      <c r="H35" s="115"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="130"/>
+      <c r="H35" s="131"/>
     </row>
     <row r="36" spans="2:8" ht="38.549999999999997" customHeight="1">
-      <c r="B36" s="116" t="s">
+      <c r="B36" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="117"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
-      <c r="H36" s="119"/>
+      <c r="C36" s="133"/>
+      <c r="D36" s="134"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="134"/>
+      <c r="G36" s="134"/>
+      <c r="H36" s="135"/>
     </row>
     <row r="37" spans="2:8" ht="19.8">
-      <c r="B37" s="123" t="s">
+      <c r="B37" s="139" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="123"/>
-      <c r="D37" s="120"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="120"/>
-      <c r="H37" s="121"/>
+      <c r="C37" s="139"/>
+      <c r="D37" s="136"/>
+      <c r="E37" s="136"/>
+      <c r="F37" s="136"/>
+      <c r="G37" s="136"/>
+      <c r="H37" s="137"/>
     </row>
     <row r="38" spans="2:8" ht="19.8">
-      <c r="B38" s="124" t="s">
+      <c r="B38" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="124"/>
-      <c r="D38" s="120"/>
-      <c r="E38" s="120"/>
-      <c r="F38" s="120"/>
-      <c r="G38" s="120"/>
-      <c r="H38" s="121"/>
+      <c r="C38" s="140"/>
+      <c r="D38" s="136"/>
+      <c r="E38" s="136"/>
+      <c r="F38" s="136"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="137"/>
     </row>
     <row r="39" spans="2:8" ht="19.8">
-      <c r="B39" s="124" t="s">
+      <c r="B39" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="124"/>
-      <c r="D39" s="122"/>
-      <c r="E39" s="120"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="120"/>
-      <c r="H39" s="121"/>
+      <c r="C39" s="140"/>
+      <c r="D39" s="138"/>
+      <c r="E39" s="136"/>
+      <c r="F39" s="136"/>
+      <c r="G39" s="136"/>
+      <c r="H39" s="137"/>
     </row>
     <row r="40" spans="2:8" ht="14.55" customHeight="1">
-      <c r="B40" s="132" t="s">
+      <c r="B40" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="133"/>
-      <c r="D40" s="129" t="s">
+      <c r="C40" s="149"/>
+      <c r="D40" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="E40" s="140" t="s">
+      <c r="E40" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="F40" s="114"/>
-      <c r="G40" s="114"/>
-      <c r="H40" s="115"/>
+      <c r="F40" s="130"/>
+      <c r="G40" s="130"/>
+      <c r="H40" s="131"/>
     </row>
     <row r="41" spans="2:8" ht="18.45" customHeight="1">
-      <c r="B41" s="134"/>
-      <c r="C41" s="135"/>
-      <c r="D41" s="130"/>
-      <c r="E41" s="125" t="s">
+      <c r="B41" s="150"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="146"/>
+      <c r="E41" s="141" t="s">
         <v>27</v>
       </c>
-      <c r="F41" s="126"/>
-      <c r="G41" s="125" t="s">
+      <c r="F41" s="142"/>
+      <c r="G41" s="141" t="s">
         <v>29</v>
       </c>
-      <c r="H41" s="126"/>
+      <c r="H41" s="142"/>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
-      <c r="B42" s="134"/>
-      <c r="C42" s="135"/>
-      <c r="D42" s="130"/>
-      <c r="E42" s="138" t="s">
+      <c r="B42" s="150"/>
+      <c r="C42" s="151"/>
+      <c r="D42" s="146"/>
+      <c r="E42" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="139"/>
-      <c r="G42" s="138" t="s">
+      <c r="F42" s="155"/>
+      <c r="G42" s="154" t="s">
         <v>30</v>
       </c>
-      <c r="H42" s="139"/>
+      <c r="H42" s="155"/>
     </row>
     <row r="43" spans="2:8" ht="15" customHeight="1">
-      <c r="B43" s="134"/>
-      <c r="C43" s="135"/>
-      <c r="D43" s="130"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="22"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="151"/>
+      <c r="D43" s="146"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="23"/>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="136"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="131"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="23"/>
+      <c r="B44" s="152"/>
+      <c r="C44" s="153"/>
+      <c r="D44" s="147"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="24"/>
     </row>
     <row r="45" spans="2:8" ht="28.2" customHeight="1">
-      <c r="B45" s="125" t="s">
+      <c r="B45" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="C45" s="126"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="21"/>
+      <c r="C45" s="142"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="22"/>
     </row>
     <row r="46" spans="2:8" ht="15.45" customHeight="1">
-      <c r="B46" s="127"/>
-      <c r="C46" s="128"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="23"/>
+      <c r="B46" s="143"/>
+      <c r="C46" s="144"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -5962,7 +6015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55481085-B667-4670-99A2-386AD4920D8B}">
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -5985,216 +6038,221 @@
       </c>
     </row>
     <row r="3" spans="1:11" hidden="1">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="59" t="s">
+      <c r="I3" s="62" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16.8" hidden="1" customHeight="1">
-      <c r="A4" s="60">
+      <c r="A4" s="63">
         <f ca="1">TODAY()</f>
-        <v>45005</v>
-      </c>
-      <c r="B4" s="59">
+        <v>44867</v>
+      </c>
+      <c r="B4" s="62">
         <v>123</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="59">
+      <c r="H4" s="62">
         <v>500</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="62">
         <v>135</v>
       </c>
-      <c r="J4" s="55"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:11" hidden="1"/>
     <row r="6" spans="1:11" hidden="1"/>
     <row r="7" spans="1:11" hidden="1"/>
     <row r="9" spans="1:11">
-      <c r="C9" s="161" t="s">
+      <c r="C9" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="161"/>
-      <c r="I9" s="161"/>
-      <c r="J9" s="161"/>
-      <c r="K9" s="161"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="177"/>
+      <c r="F9" s="177"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="177"/>
+      <c r="I9" s="177"/>
+      <c r="J9" s="177"/>
+      <c r="K9" s="177"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="K10" s="37">
+      <c r="K10" s="38">
         <f ca="1">TODAY()</f>
-        <v>45005</v>
+        <v>44867</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" thickBot="1">
-      <c r="I11" s="37"/>
+      <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="39" t="e">
+      <c r="D12" s="40" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="39" t="e">
+      <c r="F12" s="40" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G12" s="40" t="s">
+      <c r="G12" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="39" t="e">
+      <c r="H12" s="40" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="41" t="e">
+      <c r="J12" s="42" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="K12" s="49" t="s">
+      <c r="K12" s="52" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="D13" t="e">
+      <c r="D13" s="44" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E13" s="65" t="s">
+      <c r="E13" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="36" t="e">
+      <c r="F13" s="73" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G13" s="65" t="s">
+      <c r="G13" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="H13" t="e">
+      <c r="H13" s="44" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="I13" s="42" t="s">
+      <c r="I13" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="43" t="e">
+      <c r="J13" s="46" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="K13" s="50" t="e">
+      <c r="K13" s="53" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="45" t="e">
+      <c r="D14" s="48" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="45" t="e">
+      <c r="F14" s="48" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="47.55" customHeight="1">
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="56" t="s">
+      <c r="I16" s="59" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="31.8" customHeight="1">
-      <c r="C18" s="51" t="s">
+    <row r="18" spans="2:15" ht="31.8" customHeight="1">
+      <c r="C18" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="51" t="s">
+      <c r="G18" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="51" t="s">
+      <c r="H18" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="51" t="s">
+      <c r="I18" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="J18" s="51" t="s">
+      <c r="J18" s="64" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="2:14">
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+    </row>
+    <row r="19" spans="2:15">
       <c r="B19">
         <v>1</v>
       </c>
@@ -6210,7 +6268,7 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="F19" s="53" t="e">
+      <c r="F19" s="56" t="e">
         <f>(D19/$J$12)</f>
         <v>#REF!</v>
       </c>
@@ -6218,15 +6276,19 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="J19" s="66" t="e">
+      <c r="J19" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="N19" t="s">
+      <c r="K19" s="45"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="20" spans="2:14">
+      <c r="O19" s="45"/>
+    </row>
+    <row r="20" spans="2:15">
       <c r="B20">
         <v>2</v>
       </c>
@@ -6242,7 +6304,7 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="F20" s="53" t="e">
+      <c r="F20" s="56" t="e">
         <f>(D20/$J$12)</f>
         <v>#REF!</v>
       </c>
@@ -6250,15 +6312,19 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="J20" s="66" t="e">
+      <c r="J20" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="N20" t="s">
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="21" spans="2:14" ht="15.45" customHeight="1">
+      <c r="O20" s="45"/>
+    </row>
+    <row r="21" spans="2:15" ht="15.45" customHeight="1">
       <c r="B21">
         <v>3</v>
       </c>
@@ -6274,7 +6340,7 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="F21" s="53" t="e">
+      <c r="F21" s="56" t="e">
         <f>(D21/$J$12)</f>
         <v>#REF!</v>
       </c>
@@ -6282,80 +6348,110 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="J21" s="66" t="e">
+      <c r="J21" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="K21" s="61"/>
-      <c r="N21" t="s">
+      <c r="K21" s="65"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="22" spans="2:14" ht="15.45" customHeight="1">
-      <c r="K22" s="61"/>
-    </row>
-    <row r="23" spans="2:14" ht="15.45" customHeight="1">
-      <c r="K23" s="61"/>
-    </row>
-    <row r="24" spans="2:14" ht="19.8">
-      <c r="J24" s="57"/>
-      <c r="K24" s="61"/>
-    </row>
-    <row r="25" spans="2:14">
-      <c r="C25" s="36" t="s">
+      <c r="O21" s="45"/>
+    </row>
+    <row r="22" spans="2:15" ht="15.45" customHeight="1">
+      <c r="K22" s="65"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+    </row>
+    <row r="23" spans="2:15" ht="15.45" customHeight="1">
+      <c r="K23" s="65"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+    </row>
+    <row r="24" spans="2:15" ht="19.8">
+      <c r="J24" s="60"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="C25" s="37" t="s">
         <v>21</v>
       </c>
       <c r="D25" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J25" s="58"/>
-    </row>
-    <row r="26" spans="2:14" hidden="1">
-      <c r="C26" s="36" t="s">
+      <c r="J25" s="61"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+    </row>
+    <row r="26" spans="2:15" hidden="1">
+      <c r="C26" s="37" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="27" spans="2:14">
-      <c r="C27" s="36"/>
-    </row>
-    <row r="28" spans="2:14">
-      <c r="C28" s="63" t="s">
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="C27" s="37"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="C28" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="162"/>
-      <c r="E28" s="163"/>
-      <c r="F28" s="163"/>
-      <c r="G28" s="163"/>
-      <c r="H28" s="164"/>
-    </row>
-    <row r="29" spans="2:14">
-      <c r="C29" s="63"/>
-      <c r="D29" s="165"/>
-      <c r="E29" s="166"/>
-      <c r="F29" s="166"/>
-      <c r="G29" s="166"/>
-      <c r="H29" s="167"/>
-    </row>
-    <row r="30" spans="2:14">
-      <c r="C30" s="63"/>
-      <c r="D30" s="64"/>
-      <c r="E30" s="64"/>
-      <c r="F30" s="64"/>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-    </row>
-    <row r="31" spans="2:14">
-      <c r="C31" s="63" t="s">
+      <c r="D28" s="178"/>
+      <c r="E28" s="179"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="180"/>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="C29" s="67"/>
+      <c r="D29" s="181"/>
+      <c r="E29" s="182"/>
+      <c r="F29" s="182"/>
+      <c r="G29" s="182"/>
+      <c r="H29" s="183"/>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="C30" s="67"/>
+      <c r="D30" s="68"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="68"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="68"/>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="C31" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="64" t="s">
+      <c r="D31" s="68" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="64"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6516,7 +6612,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C953C335-1841-4362-90C3-1935F09A6F73}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
@@ -6538,216 +6634,221 @@
       </c>
     </row>
     <row r="3" spans="1:11" hidden="1">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="59" t="s">
+      <c r="I3" s="62" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="16.8" hidden="1" customHeight="1">
-      <c r="A4" s="60">
+      <c r="A4" s="63">
         <f ca="1">TODAY()</f>
-        <v>45005</v>
-      </c>
-      <c r="B4" s="59">
+        <v>44867</v>
+      </c>
+      <c r="B4" s="62">
         <v>123</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="62" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="59">
+      <c r="H4" s="62">
         <v>500</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="62">
         <v>135</v>
       </c>
-      <c r="J4" s="55"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="1:11" hidden="1"/>
     <row r="6" spans="1:11" hidden="1"/>
     <row r="7" spans="1:11" hidden="1"/>
     <row r="9" spans="1:11">
-      <c r="C9" s="161" t="s">
+      <c r="C9" s="177" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
-      <c r="F9" s="161"/>
-      <c r="G9" s="161"/>
-      <c r="H9" s="161"/>
-      <c r="I9" s="161"/>
-      <c r="J9" s="161"/>
-      <c r="K9" s="161"/>
+      <c r="D9" s="177"/>
+      <c r="E9" s="177"/>
+      <c r="F9" s="177"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="177"/>
+      <c r="I9" s="177"/>
+      <c r="J9" s="177"/>
+      <c r="K9" s="177"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="K10" s="37">
+      <c r="K10" s="38">
         <f ca="1">TODAY()</f>
-        <v>45005</v>
+        <v>44867</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15" thickBot="1">
-      <c r="I11" s="37"/>
+      <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="39" t="e">
+      <c r="D12" s="40" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="E12" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="39" t="e">
+      <c r="F12" s="40" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G12" s="40" t="s">
+      <c r="G12" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="39" t="e">
+      <c r="H12" s="40" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="41" t="e">
+      <c r="J12" s="42" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="K12" s="49" t="s">
+      <c r="K12" s="52" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="D13" t="e">
+      <c r="D13" s="44" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E13" s="65" t="s">
+      <c r="E13" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="F13" t="e">
+      <c r="F13" s="44" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G13" s="65" t="s">
+      <c r="G13" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="H13" t="e">
+      <c r="H13" s="44" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="I13" s="42" t="s">
+      <c r="I13" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="43" t="e">
+      <c r="J13" s="46" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="K13" s="50" t="e">
+      <c r="K13" s="53" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15" thickBot="1">
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="45" t="e">
+      <c r="D14" s="48" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="F14" s="45" t="e">
+      <c r="F14" s="48" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="51"/>
     </row>
     <row r="16" spans="1:11" ht="47.55" customHeight="1">
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="52" t="s">
+      <c r="H16" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="56" t="s">
+      <c r="I16" s="59" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="31.8" customHeight="1">
-      <c r="C18" s="51" t="s">
+    <row r="18" spans="2:15" ht="31.8" customHeight="1">
+      <c r="C18" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="51" t="s">
+      <c r="E18" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="51" t="s">
+      <c r="F18" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="51" t="s">
+      <c r="G18" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="51" t="s">
+      <c r="H18" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="51" t="s">
+      <c r="I18" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="J18" s="51" t="s">
+      <c r="J18" s="64" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="19" spans="2:11">
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+    </row>
+    <row r="19" spans="2:15">
       <c r="B19">
         <v>1</v>
       </c>
@@ -6763,7 +6864,7 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="F19" s="53" t="e">
+      <c r="F19" s="56" t="e">
         <f>(D19/$J$12)</f>
         <v>#REF!</v>
       </c>
@@ -6771,12 +6872,17 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="J19" s="66" t="e">
+      <c r="J19" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="20" spans="2:11">
+      <c r="K19" s="45"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="45"/>
+    </row>
+    <row r="20" spans="2:15">
       <c r="B20">
         <v>2</v>
       </c>
@@ -6792,7 +6898,7 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="F20" s="53" t="e">
+      <c r="F20" s="56" t="e">
         <f>(D20/$J$12)</f>
         <v>#REF!</v>
       </c>
@@ -6800,12 +6906,17 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="J20" s="66" t="e">
+      <c r="J20" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-    </row>
-    <row r="21" spans="2:11" ht="15.45" customHeight="1">
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
+    </row>
+    <row r="21" spans="2:15" ht="15.45" customHeight="1">
       <c r="B21">
         <v>3</v>
       </c>
@@ -6821,7 +6932,7 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="F21" s="53" t="e">
+      <c r="F21" s="56" t="e">
         <f>(D21/$J$12)</f>
         <v>#REF!</v>
       </c>
@@ -6829,109 +6940,150 @@
         <f>IF(ISBLANK(#REF!),"",#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="J21" s="66" t="e">
+      <c r="J21" s="72" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="K21" s="61"/>
-    </row>
-    <row r="22" spans="2:11" ht="15.45" customHeight="1">
-      <c r="K22" s="61"/>
-    </row>
-    <row r="23" spans="2:11" ht="15.45" customHeight="1">
-      <c r="K23" s="61"/>
-    </row>
-    <row r="24" spans="2:11" ht="19.8">
-      <c r="J24" s="57"/>
-      <c r="K24" s="61"/>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="C25" s="36" t="s">
+      <c r="K21" s="65"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+    </row>
+    <row r="22" spans="2:15" ht="15.45" customHeight="1">
+      <c r="K22" s="65"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="45"/>
+      <c r="O22" s="45"/>
+    </row>
+    <row r="23" spans="2:15" ht="15.45" customHeight="1">
+      <c r="K23" s="65"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+    </row>
+    <row r="24" spans="2:15" ht="19.8">
+      <c r="J24" s="60"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
+      <c r="O24" s="45"/>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="C25" s="37" t="s">
         <v>21</v>
       </c>
       <c r="D25" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J25" s="58"/>
-    </row>
-    <row r="26" spans="2:11" hidden="1">
-      <c r="C26" s="36" t="s">
+      <c r="J25" s="61"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="45"/>
+      <c r="N25" s="45"/>
+      <c r="O25" s="45"/>
+    </row>
+    <row r="26" spans="2:15" hidden="1">
+      <c r="C26" s="37" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="C27" s="36"/>
-    </row>
-    <row r="28" spans="2:11">
-      <c r="C28" s="36" t="s">
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="O26" s="45"/>
+    </row>
+    <row r="27" spans="2:15">
+      <c r="C27" s="37"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="45"/>
+      <c r="M27" s="45"/>
+      <c r="N27" s="45"/>
+      <c r="O27" s="45"/>
+    </row>
+    <row r="28" spans="2:15">
+      <c r="C28" s="70" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="168" t="str">
+      <c r="D28" s="184" t="str">
         <f>IF(ISBLANK(QC!D28),"",QC!D28)</f>
         <v/>
       </c>
-      <c r="E28" s="169"/>
-      <c r="F28" s="169"/>
-      <c r="G28" s="169"/>
-      <c r="H28" s="170"/>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="C29" s="36"/>
-      <c r="D29" s="171"/>
-      <c r="E29" s="172"/>
-      <c r="F29" s="172"/>
-      <c r="G29" s="172"/>
-      <c r="H29" s="173"/>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="C30" s="36"/>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="C31" s="36" t="s">
+      <c r="E28" s="185"/>
+      <c r="F28" s="185"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="186"/>
+    </row>
+    <row r="29" spans="2:15">
+      <c r="C29" s="70"/>
+      <c r="D29" s="187"/>
+      <c r="E29" s="188"/>
+      <c r="F29" s="188"/>
+      <c r="G29" s="188"/>
+      <c r="H29" s="189"/>
+    </row>
+    <row r="30" spans="2:15">
+      <c r="C30" s="70"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+    </row>
+    <row r="31" spans="2:15">
+      <c r="C31" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="D31" t="str">
+      <c r="D31" s="71" t="str">
         <f>QC!D31</f>
         <v>Tom</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="F31" t="str">
+      <c r="F31" s="71" t="str">
         <f>D34</f>
         <v>Mr.Donut</v>
       </c>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="C32" s="174" t="s">
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+    </row>
+    <row r="32" spans="2:15">
+      <c r="C32" s="190" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="64"/>
-      <c r="E32" s="64"/>
-      <c r="F32" s="64"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="64"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
     </row>
     <row r="33" spans="3:8">
-      <c r="C33" s="174"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
+      <c r="C33" s="190"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="68"/>
+      <c r="H33" s="68"/>
     </row>
     <row r="34" spans="3:8">
-      <c r="C34" t="s">
+      <c r="C34" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="F34" s="67">
+      <c r="E34" s="71"/>
+      <c r="F34" s="74">
         <f ca="1">TODAY()</f>
-        <v>45005</v>
-      </c>
+        <v>44867</v>
+      </c>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7154,40 +7306,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="70" t="s">
+      <c r="C1" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="71" t="s">
+      <c r="F1" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="71" t="s">
+      <c r="G1" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="78" t="s">
         <v>94</v>
       </c>
-      <c r="J1" s="71" t="s">
+      <c r="J1" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="K1" s="71" t="s">
+      <c r="K1" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="71" t="s">
+      <c r="L1" s="78" t="s">
         <v>90</v>
       </c>
       <c r="O1">
@@ -7196,51 +7348,51 @@
       </c>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="72" t="e">
+      <c r="A2" s="79" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B2" s="72" t="e">
+      <c r="B2" s="79" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="C2" s="72" t="e">
+      <c r="C2" s="79" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D2" s="72" t="e">
+      <c r="D2" s="79" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="E2" s="72" t="e">
+      <c r="E2" s="79" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F2" s="72" t="e">
+      <c r="F2" s="79" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="G2" s="72" t="e">
+      <c r="G2" s="79" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="H2" s="72" t="e">
+      <c r="H2" s="79" t="e">
         <f t="shared" ref="H2:H7" si="0">G2-L2</f>
         <v>#REF!</v>
       </c>
-      <c r="I2" s="72" t="e">
+      <c r="I2" s="79" t="e">
         <f t="shared" ref="I2:I7" si="1">H2+J2</f>
         <v>#REF!</v>
       </c>
-      <c r="J2" s="72" t="e">
+      <c r="J2" s="79" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="K2" s="72" t="e">
+      <c r="K2" s="79" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="L2" s="72" t="e">
+      <c r="L2" s="79" t="e">
         <f t="shared" ref="L2:L7" si="2">J2+K2</f>
         <v>#REF!</v>
       </c>
@@ -7249,86 +7401,86 @@
       </c>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="79" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="79" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="72" t="s">
+      <c r="D3" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="72">
+      <c r="E3" s="79">
         <v>3506</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="G3" s="72">
+      <c r="G3" s="79">
         <v>620</v>
       </c>
-      <c r="H3" s="72">
+      <c r="H3" s="79">
         <f t="shared" si="0"/>
         <v>580</v>
       </c>
-      <c r="I3" s="72">
+      <c r="I3" s="79">
         <f t="shared" si="1"/>
         <v>590</v>
       </c>
-      <c r="J3" s="72">
+      <c r="J3" s="79">
         <v>10</v>
       </c>
-      <c r="K3" s="72">
+      <c r="K3" s="79">
         <v>30</v>
       </c>
-      <c r="L3" s="72">
+      <c r="L3" s="79">
         <f t="shared" si="2"/>
         <v>40</v>
       </c>
-      <c r="P3" s="62" t="s">
+      <c r="P3" s="66" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="79" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="72" t="s">
+      <c r="B4" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="79" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="72" t="s">
+      <c r="D4" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="72">
+      <c r="E4" s="79">
         <v>3506</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="72">
+      <c r="G4" s="79">
         <v>600</v>
       </c>
-      <c r="H4" s="72">
+      <c r="H4" s="79">
         <f t="shared" si="0"/>
         <v>550</v>
       </c>
-      <c r="I4" s="72">
+      <c r="I4" s="79">
         <f t="shared" si="1"/>
         <v>570</v>
       </c>
-      <c r="J4" s="72">
+      <c r="J4" s="79">
         <v>20</v>
       </c>
-      <c r="K4" s="72">
+      <c r="K4" s="79">
         <v>30</v>
       </c>
-      <c r="L4" s="72">
+      <c r="L4" s="79">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
@@ -7340,42 +7492,42 @@
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="79" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="79">
         <v>3506</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="72">
+      <c r="G5" s="79">
         <v>610</v>
       </c>
-      <c r="H5" s="72">
+      <c r="H5" s="79">
         <f t="shared" si="0"/>
         <v>585</v>
       </c>
-      <c r="I5" s="72">
+      <c r="I5" s="79">
         <f t="shared" si="1"/>
         <v>605</v>
       </c>
-      <c r="J5" s="72">
+      <c r="J5" s="79">
         <v>20</v>
       </c>
-      <c r="K5" s="72">
+      <c r="K5" s="79">
         <v>5</v>
       </c>
-      <c r="L5" s="72">
+      <c r="L5" s="79">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
@@ -7387,42 +7539,42 @@
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="72" t="s">
+      <c r="A6" s="79" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="79" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="72" t="s">
+      <c r="D6" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="72">
+      <c r="E6" s="79">
         <v>3506</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="F6" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="72">
+      <c r="G6" s="79">
         <v>1225</v>
       </c>
-      <c r="H6" s="72">
+      <c r="H6" s="79">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="I6" s="72">
+      <c r="I6" s="79">
         <f t="shared" si="1"/>
         <v>1210</v>
       </c>
-      <c r="J6" s="72">
+      <c r="J6" s="79">
         <v>10</v>
       </c>
-      <c r="K6" s="72">
+      <c r="K6" s="79">
         <v>15</v>
       </c>
-      <c r="L6" s="72">
+      <c r="L6" s="79">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
@@ -7434,42 +7586,42 @@
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="72" t="s">
+      <c r="A7" s="79" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="72">
+      <c r="E7" s="79">
         <v>3506</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="72">
+      <c r="G7" s="79">
         <v>1225</v>
       </c>
-      <c r="H7" s="72">
+      <c r="H7" s="79">
         <f t="shared" si="0"/>
         <v>1215</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="79">
         <f t="shared" si="1"/>
         <v>1220</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="79">
         <v>5</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="79">
         <v>5</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="79">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -7484,7 +7636,7 @@
       </c>
     </row>
     <row r="9" spans="1:21" ht="28.8">
-      <c r="O9" s="68" t="s">
+      <c r="O9" s="75" t="s">
         <v>95</v>
       </c>
       <c r="Q9" t="s">
@@ -7504,25 +7656,25 @@
       </c>
     </row>
     <row r="10" spans="1:21">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="84" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="76" t="s">
+      <c r="B10" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="74" t="s">
+      <c r="C10" s="79"/>
+      <c r="D10" s="81" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="76" t="s">
+      <c r="E10" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
       <c r="Q10">
         <f>R5+R6+R7</f>
         <v>700</v>
@@ -7541,121 +7693,121 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:21" s="69" customFormat="1" ht="12">
-      <c r="A11" s="73" t="s">
+    <row r="11" spans="1:21" s="76" customFormat="1" ht="12">
+      <c r="A11" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="73" t="s">
+      <c r="D11" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="E11" s="80" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="73" t="s">
+      <c r="F11" s="80" t="s">
         <v>99</v>
       </c>
-      <c r="G11" s="73" t="s">
+      <c r="G11" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="H11" s="73" t="s">
+      <c r="H11" s="80" t="s">
         <v>102</v>
       </c>
-      <c r="I11" s="73" t="s">
+      <c r="I11" s="80" t="s">
         <v>107</v>
       </c>
-      <c r="J11" s="73" t="s">
+      <c r="J11" s="80" t="s">
         <v>108</v>
       </c>
-      <c r="K11" s="73" t="s">
+      <c r="K11" s="80" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="74">
+      <c r="B12" s="81">
         <v>3506</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="72" t="e">
+      <c r="D12" s="79" t="e">
         <f>SUM(G2:G5)</f>
         <v>#REF!</v>
       </c>
-      <c r="E12" s="72" t="e">
+      <c r="E12" s="79" t="e">
         <f>SUM(H2:H5)</f>
         <v>#REF!</v>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="79">
         <v>2400</v>
       </c>
-      <c r="G12" s="72" t="e">
+      <c r="G12" s="79" t="e">
         <f>SUM(I2:I5)</f>
         <v>#REF!</v>
       </c>
-      <c r="H12" s="75" t="e">
+      <c r="H12" s="82" t="e">
         <f>IF(F12-G12&lt;=0,"",F12-G12)</f>
         <v>#REF!</v>
       </c>
-      <c r="I12" s="72" t="e">
+      <c r="I12" s="79" t="e">
         <f>SUM(J2:J5)</f>
         <v>#REF!</v>
       </c>
-      <c r="J12" s="72" t="e">
+      <c r="J12" s="79" t="e">
         <f>SUM(K2:K5)</f>
         <v>#REF!</v>
       </c>
-      <c r="K12" s="72" t="e">
+      <c r="K12" s="79" t="e">
         <f>SUM(L2:L5)</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="13" spans="1:21">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="72">
+      <c r="B13" s="79">
         <v>3506</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="79" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="72">
+      <c r="D13" s="79">
         <f>SUM(G6:G7)</f>
         <v>2450</v>
       </c>
-      <c r="E13" s="72">
+      <c r="E13" s="79">
         <f>SUM(H6:H7)</f>
         <v>2415</v>
       </c>
-      <c r="F13" s="72">
+      <c r="F13" s="79">
         <v>2400</v>
       </c>
-      <c r="G13" s="72">
+      <c r="G13" s="79">
         <f>SUM(I6:I7)</f>
         <v>2430</v>
       </c>
-      <c r="H13" s="72" t="str">
+      <c r="H13" s="79" t="str">
         <f>IF(F13-G13&lt;=0,"",F13-G13)</f>
         <v/>
       </c>
-      <c r="I13" s="72">
+      <c r="I13" s="79">
         <f>SUM(J6:J7)</f>
         <v>15</v>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="79">
         <f>SUM(K6:K7)</f>
         <v>20</v>
       </c>
-      <c r="K13" s="72">
+      <c r="K13" s="79">
         <f>SUM(L6:L7)</f>
         <v>35</v>
       </c>
@@ -7669,430 +7821,527 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F071FA6C-DDCC-42AA-A223-D649DAB0487B}">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.44140625" style="55" customWidth="1"/>
-    <col min="2" max="2" width="57.44140625" style="55" customWidth="1"/>
-    <col min="3" max="3" width="12" style="78" customWidth="1"/>
-    <col min="4" max="4" width="52" style="55" customWidth="1"/>
-    <col min="5" max="5" width="97.5546875" style="55" customWidth="1"/>
-    <col min="6" max="16384" width="8.77734375" style="55"/>
+    <col min="1" max="1" width="8.44140625" style="58" customWidth="1"/>
+    <col min="2" max="2" width="57.44140625" style="58" customWidth="1"/>
+    <col min="3" max="3" width="12" style="85" customWidth="1"/>
+    <col min="4" max="4" width="52" style="58" customWidth="1"/>
+    <col min="5" max="5" width="97.5546875" style="58" customWidth="1"/>
+    <col min="6" max="16384" width="8.77734375" style="58"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="92" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="84"/>
-    </row>
-    <row r="2" spans="1:5" s="82" customFormat="1" ht="19.95" customHeight="1">
-      <c r="A2" s="109" t="s">
+      <c r="B1" s="91"/>
+    </row>
+    <row r="2" spans="1:5" s="89" customFormat="1" ht="19.95" customHeight="1">
+      <c r="A2" s="125" t="s">
         <v>217</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="83"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="90"/>
     </row>
     <row r="3" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="126" t="s">
         <v>216</v>
       </c>
-      <c r="B3" s="88"/>
+      <c r="B3" s="95"/>
     </row>
     <row r="4" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="126" t="s">
         <v>215</v>
       </c>
-      <c r="B4" s="88"/>
+      <c r="B4" s="95"/>
     </row>
     <row r="5" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A5" s="110" t="s">
+      <c r="A5" s="126" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="88"/>
+      <c r="B5" s="95"/>
     </row>
     <row r="6" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A6" s="110" t="s">
+      <c r="A6" s="126" t="s">
         <v>213</v>
       </c>
-      <c r="B6" s="88"/>
+      <c r="B6" s="95"/>
     </row>
     <row r="8" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A8" s="86"/>
-      <c r="B8" s="86" t="s">
+      <c r="A8" s="93"/>
+      <c r="B8" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="87"/>
-      <c r="D8" s="86" t="s">
+      <c r="C8" s="94"/>
+      <c r="D8" s="93" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="93" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A9" s="79">
+      <c r="A9" s="86">
         <v>1</v>
       </c>
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="86" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="105" t="s">
+      <c r="C9" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="D9" s="106" t="s">
+      <c r="D9" s="117" t="s">
         <v>147</v>
       </c>
-      <c r="E9" s="107" t="s">
+      <c r="E9" s="118" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A10" s="80"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="105" t="s">
+      <c r="A10" s="87"/>
+      <c r="B10" s="87"/>
+      <c r="C10" s="116" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="D10" s="117" t="s">
         <v>139</v>
       </c>
-      <c r="E10" s="107" t="s">
+      <c r="E10" s="118" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A11" s="80"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="105" t="s">
+      <c r="A11" s="87"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="116" t="s">
         <v>114</v>
       </c>
-      <c r="D11" s="106" t="s">
+      <c r="D11" s="117" t="s">
         <v>150</v>
       </c>
-      <c r="E11" s="107" t="s">
+      <c r="E11" s="118" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A12" s="80"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="105" t="s">
+      <c r="A12" s="87"/>
+      <c r="B12" s="87"/>
+      <c r="C12" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="106" t="s">
+      <c r="D12" s="117" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="107"/>
+      <c r="E12" s="118"/>
     </row>
     <row r="13" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A13" s="80"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="105" t="s">
+      <c r="A13" s="87"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="106" t="s">
+      <c r="D13" s="117" t="s">
         <v>141</v>
       </c>
-      <c r="E13" s="107"/>
+      <c r="E13" s="118"/>
     </row>
     <row r="14" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A14" s="80"/>
-      <c r="B14" s="80"/>
-      <c r="C14" s="105" t="s">
+      <c r="A14" s="87"/>
+      <c r="B14" s="87"/>
+      <c r="C14" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="106" t="s">
+      <c r="D14" s="117" t="s">
         <v>152</v>
       </c>
-      <c r="E14" s="107"/>
+      <c r="E14" s="118"/>
     </row>
     <row r="15" spans="1:5" ht="28.8" customHeight="1">
-      <c r="A15" s="80"/>
-      <c r="B15" s="80"/>
-      <c r="C15" s="105" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="106" t="s">
+      <c r="D15" s="117" t="s">
         <v>142</v>
       </c>
-      <c r="E15" s="108" t="s">
+      <c r="E15" s="119" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="29.4" customHeight="1">
-      <c r="A16" s="80"/>
-      <c r="B16" s="80"/>
-      <c r="C16" s="105" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="104" t="s">
+      <c r="D16" s="115" t="s">
         <v>153</v>
       </c>
-      <c r="E16" s="107" t="s">
+      <c r="E16" s="118" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A17" s="80"/>
-      <c r="B17" s="80"/>
-      <c r="C17" s="105" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="116" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="106" t="s">
+      <c r="D17" s="117" t="s">
         <v>144</v>
       </c>
-      <c r="E17" s="107"/>
+      <c r="E17" s="118"/>
     </row>
     <row r="18" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A18" s="80"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="105" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="116" t="s">
         <v>121</v>
       </c>
-      <c r="D18" s="106" t="s">
+      <c r="D18" s="117" t="s">
         <v>154</v>
       </c>
-      <c r="E18" s="107" t="s">
+      <c r="E18" s="118" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="28.2" customHeight="1">
-      <c r="A19" s="80"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="105" t="s">
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="116" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="104" t="s">
+      <c r="D19" s="115" t="s">
         <v>155</v>
       </c>
-      <c r="E19" s="107" t="s">
+      <c r="E19" s="118" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="220.2" customHeight="1">
-      <c r="A20" s="80"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="105" t="s">
+      <c r="A20" s="87"/>
+      <c r="B20" s="87"/>
+      <c r="C20" s="116" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="104" t="s">
+      <c r="D20" s="115" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="108" t="s">
+      <c r="E20" s="119" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="28.2" customHeight="1">
-      <c r="A21" s="80"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="105" t="s">
+      <c r="A21" s="87"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="104" t="s">
+      <c r="D21" s="115" t="s">
         <v>156</v>
       </c>
-      <c r="E21" s="107"/>
+      <c r="E21" s="118"/>
     </row>
     <row r="22" spans="1:5" ht="19.8" customHeight="1">
-      <c r="A22" s="81"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="105" t="s">
+      <c r="A22" s="88"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="116" t="s">
         <v>160</v>
       </c>
-      <c r="D22" s="106" t="s">
+      <c r="D22" s="117" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="107"/>
+      <c r="E22" s="118"/>
     </row>
     <row r="23" spans="1:5" ht="37.200000000000003" customHeight="1">
-      <c r="A23" s="102"/>
-      <c r="B23" s="102"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="93"/>
+      <c r="A23" s="112"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="113"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="102"/>
     </row>
     <row r="24" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A24" s="102"/>
-      <c r="B24" s="102"/>
-      <c r="E24" s="93"/>
+      <c r="A24" s="112"/>
+      <c r="B24" s="112"/>
+      <c r="C24" s="113"/>
+      <c r="D24" s="97"/>
+      <c r="E24" s="102"/>
     </row>
     <row r="25" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A25" s="102"/>
-      <c r="B25" s="102"/>
-      <c r="E25" s="93"/>
+      <c r="A25" s="112"/>
+      <c r="B25" s="112"/>
+      <c r="C25" s="113"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="102"/>
     </row>
     <row r="26" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A26" s="102"/>
-      <c r="B26" s="102"/>
-      <c r="E26" s="93"/>
+      <c r="A26" s="112"/>
+      <c r="B26" s="112"/>
+      <c r="C26" s="113"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="102"/>
     </row>
     <row r="27" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A27" s="102"/>
-      <c r="B27" s="102"/>
-      <c r="E27" s="93"/>
+      <c r="A27" s="112"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="102"/>
     </row>
     <row r="28" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A28" s="102"/>
-      <c r="B28" s="102"/>
-      <c r="E28" s="93"/>
+      <c r="A28" s="112"/>
+      <c r="B28" s="112"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="102"/>
     </row>
     <row r="29" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A29" s="102"/>
-      <c r="B29" s="102"/>
-      <c r="E29" s="93"/>
+      <c r="A29" s="112"/>
+      <c r="B29" s="112"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="102"/>
     </row>
     <row r="30" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A30" s="102"/>
-      <c r="B30" s="102"/>
-      <c r="E30" s="93"/>
+      <c r="A30" s="112"/>
+      <c r="B30" s="112"/>
+      <c r="C30" s="113"/>
+      <c r="D30" s="97"/>
+      <c r="E30" s="102"/>
     </row>
     <row r="31" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="102"/>
-      <c r="E31" s="93"/>
+      <c r="A31" s="112"/>
+      <c r="B31" s="112"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="102"/>
     </row>
     <row r="32" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A32" s="102"/>
-      <c r="B32" s="102"/>
-      <c r="E32" s="93"/>
+      <c r="A32" s="112"/>
+      <c r="B32" s="112"/>
+      <c r="C32" s="113"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="102"/>
     </row>
     <row r="33" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A33" s="102"/>
-      <c r="B33" s="102"/>
-      <c r="E33" s="93"/>
+      <c r="A33" s="112"/>
+      <c r="B33" s="112"/>
+      <c r="C33" s="113"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="102"/>
     </row>
     <row r="34" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A34" s="102"/>
-      <c r="B34" s="102"/>
-      <c r="E34" s="93"/>
+      <c r="A34" s="112"/>
+      <c r="B34" s="112"/>
+      <c r="C34" s="113"/>
+      <c r="D34" s="97"/>
+      <c r="E34" s="102"/>
     </row>
     <row r="35" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A35" s="102"/>
-      <c r="B35" s="102"/>
-      <c r="E35" s="93"/>
+      <c r="A35" s="112"/>
+      <c r="B35" s="112"/>
+      <c r="C35" s="113"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="102"/>
     </row>
     <row r="36" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A36" s="102"/>
-      <c r="B36" s="102"/>
-      <c r="E36" s="93"/>
+      <c r="A36" s="112"/>
+      <c r="B36" s="112"/>
+      <c r="C36" s="113"/>
+      <c r="D36" s="97"/>
+      <c r="E36" s="102"/>
     </row>
     <row r="37" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A37" s="102"/>
-      <c r="B37" s="102"/>
-      <c r="E37" s="93"/>
+      <c r="A37" s="112"/>
+      <c r="B37" s="112"/>
+      <c r="C37" s="113"/>
+      <c r="D37" s="97"/>
+      <c r="E37" s="102"/>
     </row>
     <row r="38" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A38" s="102"/>
-      <c r="B38" s="102"/>
-      <c r="E38" s="93"/>
+      <c r="A38" s="112"/>
+      <c r="B38" s="112"/>
+      <c r="C38" s="113"/>
+      <c r="D38" s="97"/>
+      <c r="E38" s="102"/>
     </row>
     <row r="39" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A39" s="102"/>
-      <c r="B39" s="102"/>
-      <c r="E39" s="93"/>
+      <c r="A39" s="112"/>
+      <c r="B39" s="112"/>
+      <c r="C39" s="113"/>
+      <c r="D39" s="97"/>
+      <c r="E39" s="102"/>
     </row>
     <row r="40" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A40" s="102"/>
-      <c r="B40" s="102"/>
-      <c r="E40" s="93"/>
+      <c r="A40" s="112"/>
+      <c r="B40" s="112"/>
+      <c r="C40" s="113"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="102"/>
     </row>
     <row r="41" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A41" s="102"/>
-      <c r="B41" s="102"/>
-      <c r="E41" s="93"/>
+      <c r="A41" s="112"/>
+      <c r="B41" s="112"/>
+      <c r="C41" s="113"/>
+      <c r="D41" s="97"/>
+      <c r="E41" s="102"/>
     </row>
     <row r="42" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A42" s="102"/>
-      <c r="B42" s="102"/>
-      <c r="E42" s="93"/>
+      <c r="A42" s="112"/>
+      <c r="B42" s="112"/>
+      <c r="C42" s="113"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="102"/>
     </row>
     <row r="43" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A43" s="102"/>
-      <c r="B43" s="102"/>
-      <c r="E43" s="93"/>
+      <c r="A43" s="112"/>
+      <c r="B43" s="112"/>
+      <c r="C43" s="113"/>
+      <c r="D43" s="97"/>
+      <c r="E43" s="102"/>
     </row>
     <row r="44" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A44" s="102"/>
-      <c r="B44" s="102"/>
-      <c r="E44" s="93"/>
+      <c r="A44" s="112"/>
+      <c r="B44" s="112"/>
+      <c r="C44" s="113"/>
+      <c r="D44" s="97"/>
+      <c r="E44" s="102"/>
     </row>
     <row r="45" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A45" s="102"/>
-      <c r="B45" s="102"/>
-      <c r="E45" s="93"/>
+      <c r="A45" s="112"/>
+      <c r="B45" s="112"/>
+      <c r="C45" s="113"/>
+      <c r="D45" s="97"/>
+      <c r="E45" s="102"/>
     </row>
     <row r="46" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A46" s="102"/>
-      <c r="B46" s="102"/>
-      <c r="E46" s="93"/>
+      <c r="A46" s="112"/>
+      <c r="B46" s="112"/>
+      <c r="C46" s="113"/>
+      <c r="D46" s="97"/>
+      <c r="E46" s="102"/>
     </row>
     <row r="47" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A47" s="102"/>
-      <c r="B47" s="102"/>
-      <c r="E47" s="93"/>
+      <c r="A47" s="112"/>
+      <c r="B47" s="112"/>
+      <c r="C47" s="113"/>
+      <c r="D47" s="97"/>
+      <c r="E47" s="102"/>
     </row>
     <row r="48" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A48" s="102"/>
-      <c r="B48" s="103"/>
-      <c r="E48" s="93"/>
+      <c r="A48" s="112"/>
+      <c r="B48" s="114"/>
+      <c r="C48" s="113"/>
+      <c r="D48" s="97"/>
+      <c r="E48" s="102"/>
     </row>
     <row r="49" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A49" s="102"/>
-      <c r="B49" s="103"/>
-      <c r="E49" s="93"/>
+      <c r="A49" s="112"/>
+      <c r="B49" s="114"/>
+      <c r="C49" s="113"/>
+      <c r="D49" s="97"/>
+      <c r="E49" s="102"/>
     </row>
     <row r="50" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A50" s="102"/>
-      <c r="B50" s="102"/>
-      <c r="E50" s="93"/>
+      <c r="A50" s="112"/>
+      <c r="B50" s="112"/>
+      <c r="C50" s="113"/>
+      <c r="D50" s="97"/>
+      <c r="E50" s="102"/>
     </row>
     <row r="51" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A51" s="102"/>
-      <c r="B51" s="102"/>
-      <c r="E51" s="93"/>
+      <c r="A51" s="112"/>
+      <c r="B51" s="112"/>
+      <c r="C51" s="113"/>
+      <c r="D51" s="97"/>
+      <c r="E51" s="102"/>
     </row>
     <row r="52" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A52" s="102"/>
-      <c r="B52" s="102"/>
-      <c r="E52" s="93"/>
+      <c r="A52" s="112"/>
+      <c r="B52" s="112"/>
+      <c r="C52" s="113"/>
+      <c r="D52" s="97"/>
+      <c r="E52" s="102"/>
     </row>
     <row r="53" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A53" s="102"/>
-      <c r="B53" s="102"/>
-      <c r="E53" s="93"/>
+      <c r="A53" s="112"/>
+      <c r="B53" s="112"/>
+      <c r="C53" s="113"/>
+      <c r="D53" s="97"/>
+      <c r="E53" s="102"/>
     </row>
     <row r="54" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A54" s="102"/>
-      <c r="B54" s="102"/>
-      <c r="E54" s="93"/>
+      <c r="A54" s="112"/>
+      <c r="B54" s="112"/>
+      <c r="C54" s="113"/>
+      <c r="D54" s="97"/>
+      <c r="E54" s="102"/>
     </row>
     <row r="55" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A55" s="102"/>
-      <c r="B55" s="102"/>
-      <c r="E55" s="93"/>
+      <c r="A55" s="112"/>
+      <c r="B55" s="112"/>
+      <c r="C55" s="113"/>
+      <c r="D55" s="97"/>
+      <c r="E55" s="102"/>
     </row>
     <row r="56" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A56" s="102"/>
-      <c r="B56" s="102"/>
-      <c r="E56" s="93"/>
+      <c r="A56" s="112"/>
+      <c r="B56" s="112"/>
+      <c r="C56" s="113"/>
+      <c r="D56" s="97"/>
+      <c r="E56" s="102"/>
     </row>
     <row r="57" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A57" s="102"/>
-      <c r="B57" s="102"/>
-      <c r="E57" s="93"/>
+      <c r="A57" s="112"/>
+      <c r="B57" s="112"/>
+      <c r="C57" s="113"/>
+      <c r="D57" s="97"/>
+      <c r="E57" s="102"/>
     </row>
     <row r="58" spans="1:5" ht="19.95" customHeight="1">
-      <c r="A58" s="102"/>
-      <c r="B58" s="102"/>
-      <c r="E58" s="93"/>
+      <c r="A58" s="112"/>
+      <c r="B58" s="112"/>
+      <c r="C58" s="113"/>
+      <c r="D58" s="97"/>
+      <c r="E58" s="102"/>
     </row>
     <row r="59" spans="1:5" ht="19.95" customHeight="1">
-      <c r="E59" s="93"/>
+      <c r="A59" s="97"/>
+      <c r="B59" s="97"/>
+      <c r="C59" s="113"/>
+      <c r="D59" s="97"/>
+      <c r="E59" s="102"/>
     </row>
     <row r="60" spans="1:5" ht="19.95" customHeight="1">
-      <c r="E60" s="93"/>
+      <c r="A60" s="97"/>
+      <c r="B60" s="97"/>
+      <c r="C60" s="113"/>
+      <c r="D60" s="97"/>
+      <c r="E60" s="102"/>
     </row>
     <row r="61" spans="1:5" ht="19.95" customHeight="1">
-      <c r="E61" s="93"/>
+      <c r="A61" s="97"/>
+      <c r="B61" s="97"/>
+      <c r="C61" s="113"/>
+      <c r="D61" s="97"/>
+      <c r="E61" s="102"/>
+    </row>
+    <row r="62" spans="1:5" ht="19.95" customHeight="1">
+      <c r="A62" s="97"/>
+      <c r="B62" s="97"/>
+      <c r="C62" s="113"/>
+      <c r="D62" s="97"/>
+      <c r="E62" s="97"/>
+    </row>
+    <row r="63" spans="1:5" ht="19.95" customHeight="1">
+      <c r="A63" s="97"/>
+      <c r="B63" s="97"/>
+      <c r="C63" s="113"/>
+      <c r="D63" s="97"/>
+      <c r="E63" s="97"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -8121,410 +8370,629 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2BCEFF2-0882-492F-A925-F8FC2418555C}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="19.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6" style="55" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" style="55" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" style="55" customWidth="1"/>
-    <col min="4" max="4" width="30.88671875" style="55" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="91" customWidth="1"/>
-    <col min="6" max="6" width="73.77734375" style="55" customWidth="1"/>
-    <col min="7" max="7" width="40.109375" style="93" customWidth="1"/>
-    <col min="8" max="16384" width="8.77734375" style="55"/>
+    <col min="1" max="1" width="6" style="58" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" style="58" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" style="58" customWidth="1"/>
+    <col min="4" max="4" width="30.88671875" style="58" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" style="99" customWidth="1"/>
+    <col min="6" max="6" width="73.77734375" style="58" customWidth="1"/>
+    <col min="7" max="7" width="40.109375" style="101" customWidth="1"/>
+    <col min="8" max="16384" width="8.77734375" style="58"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A1" s="111" t="s">
+    <row r="1" spans="1:14" ht="19.95" customHeight="1">
+      <c r="A1" s="127" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="111" t="s">
+      <c r="B1" s="127" t="s">
         <v>129</v>
       </c>
-      <c r="C1" s="111" t="s">
+      <c r="C1" s="127" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="111" t="s">
+      <c r="D1" s="127" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="128" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="111" t="s">
+      <c r="F1" s="127" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="129" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A2" s="55">
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.95" customHeight="1">
+      <c r="A2" s="58">
         <v>1</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="57" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="58" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="91">
+      <c r="E2" s="99">
         <v>0</v>
       </c>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="G2" s="93" t="s">
+      <c r="G2" s="102" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.95" customHeight="1">
-      <c r="C3" s="55" t="s">
+      <c r="H2" s="97"/>
+      <c r="I2" s="97"/>
+      <c r="J2" s="97"/>
+      <c r="K2" s="97"/>
+      <c r="L2" s="97"/>
+      <c r="M2" s="97"/>
+      <c r="N2" s="97"/>
+    </row>
+    <row r="3" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C3" s="58" t="s">
         <v>168</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="E3" s="91">
+      <c r="E3" s="99">
         <v>0</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="58" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="93" t="s">
+      <c r="G3" s="102" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A5" s="55">
+      <c r="H3" s="97"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
+    </row>
+    <row r="4" spans="1:14" ht="19.95" customHeight="1">
+      <c r="G4" s="102"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+    </row>
+    <row r="5" spans="1:14" ht="19.95" customHeight="1">
+      <c r="A5" s="58">
         <v>2</v>
       </c>
-      <c r="B5" s="55" t="s">
+      <c r="B5" s="58" t="s">
         <v>171</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="58" t="s">
         <v>172</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="91">
+      <c r="E5" s="99">
         <v>0</v>
       </c>
-      <c r="F5" s="55" t="s">
+      <c r="F5" s="58" t="s">
         <v>173</v>
       </c>
-      <c r="G5" s="93" t="s">
+      <c r="G5" s="102" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A7" s="55">
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+    </row>
+    <row r="6" spans="1:14" ht="19.95" customHeight="1">
+      <c r="G6" s="102"/>
+      <c r="H6" s="97"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="97"/>
+      <c r="M6" s="97"/>
+      <c r="N6" s="97"/>
+    </row>
+    <row r="7" spans="1:14" ht="19.95" customHeight="1">
+      <c r="A7" s="58">
         <v>3</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="58" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="91" t="s">
+      <c r="E7" s="99" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.95" customHeight="1">
-      <c r="C8" s="55" t="s">
+      <c r="G7" s="102"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+    </row>
+    <row r="8" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C8" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="E8" s="91">
+      <c r="E8" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.95" customHeight="1">
-      <c r="C9" s="55" t="s">
+      <c r="G8" s="102"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="97"/>
+      <c r="M8" s="97"/>
+      <c r="N8" s="97"/>
+    </row>
+    <row r="9" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C9" s="58" t="s">
         <v>180</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="E9" s="91">
+      <c r="E9" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.95" customHeight="1">
-      <c r="C10" s="55" t="s">
+      <c r="G9" s="102"/>
+      <c r="H9" s="97"/>
+      <c r="I9" s="97"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="97"/>
+      <c r="L9" s="97"/>
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+    </row>
+    <row r="10" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C10" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="E10" s="91">
+      <c r="E10" s="99">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.95" customHeight="1">
-      <c r="C11" s="55" t="s">
+      <c r="G10" s="102"/>
+      <c r="H10" s="97"/>
+      <c r="I10" s="97"/>
+      <c r="J10" s="97"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="97"/>
+      <c r="M10" s="97"/>
+      <c r="N10" s="97"/>
+    </row>
+    <row r="11" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C11" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="91">
+      <c r="E11" s="99">
         <v>0</v>
       </c>
-      <c r="F11" s="55" t="s">
+      <c r="F11" s="58" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.95" customHeight="1">
-      <c r="C12" s="55" t="s">
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="97"/>
+      <c r="M11" s="97"/>
+      <c r="N11" s="97"/>
+    </row>
+    <row r="12" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C12" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F12" s="55" t="s">
+      <c r="F12" s="58" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A14" s="55">
+      <c r="H12" s="97"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="97"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="97"/>
+      <c r="N12" s="97"/>
+    </row>
+    <row r="13" spans="1:14" ht="19.95" customHeight="1">
+      <c r="H13" s="97"/>
+      <c r="I13" s="97"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="97"/>
+      <c r="N13" s="97"/>
+    </row>
+    <row r="14" spans="1:14" ht="19.95" customHeight="1">
+      <c r="A14" s="58">
         <v>4</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="55" t="s">
+      <c r="C14" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="D14" s="55" t="s">
+      <c r="D14" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="E14" s="91" t="s">
+      <c r="E14" s="99" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.95" customHeight="1">
-      <c r="C15" s="55" t="s">
+      <c r="G14" s="102"/>
+      <c r="H14" s="97"/>
+      <c r="I14" s="97"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="97"/>
+      <c r="M14" s="97"/>
+      <c r="N14" s="97"/>
+    </row>
+    <row r="15" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C15" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F15" s="55" t="s">
+      <c r="F15" s="58" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.95" customHeight="1">
-      <c r="C16" s="55" t="s">
+      <c r="G15" s="102"/>
+      <c r="H15" s="97"/>
+      <c r="I15" s="97"/>
+      <c r="J15" s="97"/>
+      <c r="K15" s="97"/>
+      <c r="L15" s="97"/>
+      <c r="M15" s="97"/>
+      <c r="N15" s="97"/>
+    </row>
+    <row r="16" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C16" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D16" s="58" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C17" s="55" t="s">
+      <c r="G16" s="102"/>
+      <c r="H16" s="97"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="97"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="97"/>
+      <c r="M16" s="97"/>
+      <c r="N16" s="97"/>
+    </row>
+    <row r="17" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C17" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="F17" s="55" t="s">
+      <c r="F17" s="58" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C18" s="55" t="s">
+      <c r="G17" s="102"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="97"/>
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="97"/>
+    </row>
+    <row r="18" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C18" s="58" t="s">
         <v>190</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="F18" s="55" t="s">
+      <c r="F18" s="58" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C19" s="55" t="s">
+      <c r="G18" s="102"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="97"/>
+    </row>
+    <row r="19" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C19" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="F19" s="55" t="s">
+      <c r="F19" s="58" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C20" s="55" t="s">
+      <c r="G19" s="102"/>
+      <c r="H19" s="97"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="97"/>
+      <c r="M19" s="97"/>
+      <c r="N19" s="97"/>
+    </row>
+    <row r="20" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C20" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="F20" s="55" t="s">
+      <c r="F20" s="58" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C21" s="55" t="s">
+      <c r="G20" s="102"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="97"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="97"/>
+      <c r="N20" s="97"/>
+    </row>
+    <row r="21" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C21" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="F21" s="55" t="s">
+      <c r="F21" s="58" t="s">
         <v>203</v>
       </c>
-      <c r="H21" s="90"/>
-    </row>
-    <row r="22" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C22" s="55" t="s">
+      <c r="G21" s="102"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="97"/>
+      <c r="M21" s="97"/>
+      <c r="N21" s="97"/>
+    </row>
+    <row r="22" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C22" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="F22" s="55" t="s">
+      <c r="F22" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="H22" s="90"/>
-    </row>
-    <row r="23" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C23" s="55" t="s">
+      <c r="G22" s="102"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="97"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="97"/>
+      <c r="M22" s="97"/>
+      <c r="N22" s="97"/>
+    </row>
+    <row r="23" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C23" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="E23" s="91">
+      <c r="E23" s="99">
         <v>0</v>
       </c>
-      <c r="F23" s="55" t="s">
+      <c r="F23" s="58" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C24" s="55" t="s">
+      <c r="G23" s="102"/>
+      <c r="H23" s="97"/>
+      <c r="I23" s="97"/>
+      <c r="J23" s="97"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="97"/>
+      <c r="M23" s="97"/>
+      <c r="N23" s="97"/>
+    </row>
+    <row r="24" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C24" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="55" t="s">
+      <c r="F24" s="58" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="19.95" customHeight="1">
-      <c r="G25" s="94"/>
-    </row>
-    <row r="26" spans="1:8" ht="19.95" customHeight="1">
-      <c r="A26" s="55">
+      <c r="G24" s="102"/>
+      <c r="H24" s="97"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="97"/>
+      <c r="M24" s="97"/>
+      <c r="N24" s="97"/>
+    </row>
+    <row r="25" spans="1:14" ht="19.95" customHeight="1">
+      <c r="G25" s="103"/>
+      <c r="H25" s="97"/>
+      <c r="I25" s="97"/>
+      <c r="J25" s="97"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="97"/>
+      <c r="M25" s="97"/>
+      <c r="N25" s="97"/>
+    </row>
+    <row r="26" spans="1:14" ht="19.95" customHeight="1">
+      <c r="A26" s="58">
         <v>5</v>
       </c>
-      <c r="B26" s="55" t="s">
+      <c r="B26" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="D26" s="55" t="s">
+      <c r="D26" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="E26" s="91" t="s">
+      <c r="E26" s="99" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C27" s="55" t="s">
+      <c r="G26" s="102"/>
+      <c r="H26" s="97"/>
+      <c r="I26" s="97"/>
+      <c r="J26" s="97"/>
+      <c r="K26" s="97"/>
+      <c r="L26" s="97"/>
+      <c r="M26" s="97"/>
+      <c r="N26" s="97"/>
+    </row>
+    <row r="27" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C27" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="D27" s="55" t="s">
+      <c r="D27" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="F27" s="55" t="s">
+      <c r="F27" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="G27" s="93" t="s">
+      <c r="G27" s="102" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C28" s="55" t="s">
+      <c r="H27" s="97"/>
+      <c r="I27" s="97"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="97"/>
+      <c r="M27" s="97"/>
+      <c r="N27" s="97"/>
+    </row>
+    <row r="28" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C28" s="58" t="s">
         <v>206</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="D28" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="F28" s="55" t="s">
+      <c r="F28" s="58" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C29" s="55" t="s">
+      <c r="G28" s="102"/>
+      <c r="H28" s="97"/>
+      <c r="I28" s="97"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="97"/>
+      <c r="N28" s="97"/>
+    </row>
+    <row r="29" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C29" s="58" t="s">
         <v>207</v>
       </c>
-      <c r="D29" s="55" t="s">
+      <c r="D29" s="58" t="s">
         <v>184</v>
       </c>
-      <c r="F29" s="55" t="s">
+      <c r="F29" s="58" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C30" s="55" t="s">
+    <row r="30" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C30" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="D30" s="55" t="s">
+      <c r="D30" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="F30" s="55" t="s">
+      <c r="F30" s="58" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="19.95" customHeight="1">
-      <c r="C31" s="55" t="s">
+    <row r="31" spans="1:14" ht="19.95" customHeight="1">
+      <c r="C31" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="D31" s="55" t="s">
+      <c r="D31" s="58" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B35" s="54"/>
+      <c r="B35" s="57"/>
     </row>
     <row r="42" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B42" s="54"/>
+      <c r="B42" s="57"/>
     </row>
     <row r="47" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B47" s="54"/>
+      <c r="B47" s="57"/>
     </row>
     <row r="48" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B48" s="54"/>
+      <c r="B48" s="57"/>
     </row>
     <row r="52" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B52" s="54"/>
+      <c r="B52" s="57"/>
     </row>
     <row r="53" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B53" s="54"/>
+      <c r="B53" s="57"/>
     </row>
     <row r="57" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B57" s="54"/>
+      <c r="B57" s="57"/>
     </row>
     <row r="64" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B64" s="54"/>
+      <c r="B64" s="57"/>
     </row>
     <row r="73" spans="2:2" ht="19.95" customHeight="1">
-      <c r="B73" s="54"/>
+      <c r="B73" s="57"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
